--- a/artfynd/A 8912-2026 artfynd.xlsx
+++ b/artfynd/A 8912-2026 artfynd.xlsx
@@ -907,48 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68649333</v>
+        <v>678872</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ränneslöv-Ysby, Skenavägen1, Hl</t>
+          <t>S HULTABYGGET (04C3i14), Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391285</v>
+        <v>391474</v>
       </c>
       <c r="R4" t="n">
-        <v>6261964</v>
+        <v>6261702</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,12 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-16</t>
+          <t>1997-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-16</t>
+          <t>1997-07-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>040238141 / NECK COM / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,44 +991,42 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blandskog med bok,tall och gran</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Gunilla Hederås</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>H2017-028</t>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal bok</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Hederås</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Hederås, Jan-Erik Hederås</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>678872</v>
+        <v>1016002</v>
       </c>
       <c r="B5" t="n">
-        <v>96437</v>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>040238141 / NECK COM / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>040238141 / ANTI CUR / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1016002</v>
+        <v>91691650</v>
       </c>
       <c r="B6" t="n">
-        <v>96426</v>
+        <v>98194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,34 +1150,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>220686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S HULTABYGGET (04C3i14), Hl</t>
+          <t>Perstorps skog, Skenavägen, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>391474</v>
+        <v>391517</v>
       </c>
       <c r="R6" t="n">
-        <v>6261702</v>
+        <v>6261791</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,17 +1213,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1997-07-23</t>
+          <t>2010-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1997-07-23</t>
+          <t>2010-10-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>040238141 / ANTI CUR / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,81 +1237,66 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Gammal bok</t>
+          <t>bryn mot skogsväg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Jan-Erik Hederås</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Jan-Erik Hederås, Gunilla Hederås</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91691650</v>
+        <v>68649333</v>
       </c>
       <c r="B7" t="n">
-        <v>98194</v>
+        <v>93269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>6052576</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Boktaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hydnellum fagiscabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>A.M.Ainsw. &amp; Nitare</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Perstorps skog, Skenavägen, Hl</t>
+          <t>Ränneslöv-Ysby, Skenavägen1, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>391517</v>
+        <v>391285</v>
       </c>
       <c r="R7" t="n">
-        <v>6261791</v>
+        <v>6261964</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,17 +1323,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-10-08</t>
+          <t>2017-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-10-08</t>
+          <t>2017-09-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Från början bestämd till Sarcodon scabrosum, men ombestämd till fagiscabrosum. Biotopen lite lurig eftersom det var en bokskog med inslag av gamla tallar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,23 +1342,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>bryn mot skogsväg</t>
+          <t>blandskog med bok,tall och gran</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Gunilla Hederås</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>H2017-028</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan-Erik Hederås</t>
+          <t>Gunilla Hederås</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan-Erik Hederås, Gunilla Hederås</t>
+          <t>Gunilla Hederås, Jan-Erik Hederås</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 8912-2026 artfynd.xlsx
+++ b/artfynd/A 8912-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/275294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/398356</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1016002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91691650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68649333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,8 +1523,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68649349</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8912-2026 artfynd.xlsx
+++ b/artfynd/A 8912-2026 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>68649333</v>
       </c>
       <c r="B7" t="n">
-        <v>93269</v>
+        <v>93311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>68649349</v>
       </c>
       <c r="B8" t="n">
-        <v>93295</v>
+        <v>93337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8912-2026 artfynd.xlsx
+++ b/artfynd/A 8912-2026 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>68649333</v>
       </c>
       <c r="B7" t="n">
-        <v>93311</v>
+        <v>93338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
